--- a/output/pdf_financials_xlsx/MINE.xlsx
+++ b/output/pdf_financials_xlsx/MINE.xlsx
@@ -4978,37 +4978,37 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.04942</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.04942</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.052459</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.085448</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.116159</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.137184</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.164973</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.407357</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.364703</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.480868</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.542816</v>
       </c>
     </row>
     <row r="93">
@@ -8304,7 +8304,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11067,7 +11071,11 @@
           <t>Reserve (Note 7(e))</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -11914,7 +11922,11 @@
           <t>Reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -12813,7 +12825,11 @@
           <t>Reserve (Note 6) 49,420</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MINE.xlsx
+++ b/output/pdf_financials_xlsx/MINE.xlsx
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.004871</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.004099</v>
       </c>
     </row>
     <row r="13">
@@ -1742,10 +1742,10 @@
         <v>-0.372587</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.300826</v>
+        <v>-0.305697</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.266607</v>
+        <v>-0.270706</v>
       </c>
     </row>
     <row r="28">
@@ -1834,10 +1834,10 @@
         <v>-0.372587</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.300826</v>
+        <v>-0.305697</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.266607</v>
+        <v>-0.270706</v>
       </c>
     </row>
     <row r="30">
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.101095</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.231205</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.07947799999999999</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.436205</v>
@@ -2067,10 +2067,10 @@
         <v>0.106476</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.018831</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.378347</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.459489</v>
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.101095</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.231205</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.07947799999999999</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.436205</v>
@@ -2163,10 +2163,10 @@
         <v>0.106476</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.018831</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.378347</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.459489</v>
@@ -2721,13 +2721,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.108238</v>
+        <v>0.007143</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.231205</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.09447800000000001</v>
+        <v>0.015</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.0225</v>
@@ -2739,10 +2739,10 @@
         <v>0.049604</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.06343500000000001</v>
+        <v>0.044604</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.455847</v>
+        <v>0.0775</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.115</v>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">

--- a/output/pdf_financials_xlsx/MINE.xlsx
+++ b/output/pdf_financials_xlsx/MINE.xlsx
@@ -5864,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.034803</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
@@ -6956,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.034803</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
         <v>-0.276204</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-0.272753</v>
+        <v>-0.307556</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-0.17118</v>
@@ -14411,7 +14411,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -19697,7 +19701,11 @@
           <t>Net funds received on private placement</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -21678,7 +21686,11 @@
           <t>Shares issued in private placement $</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -23237,7 +23249,11 @@
           <t>Shares issued for cash $</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E204" s="5" t="n">
         <v>0.115</v>
       </c>
